--- a/144/DQ Templates and Instructions/Topic 6 DQ 2/Topic 6 DQ 2.xlsx
+++ b/144/DQ Templates and Instructions/Topic 6 DQ 2/Topic 6 DQ 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail.sharepoint.com/sites/MathematicsProgramFacultyStaff-MATOFTF/Shared Documents/MATOFTF/ALEKS/DQ Templates and Instructions/Topic 6 DQ 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{558D6C02-132F-4F4C-922D-FF511F69F3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{558D6C02-132F-4F4C-922D-FF511F69F3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F09CFDAD-6075-4C56-B993-2B06F414AD5A}"/>
   <bookViews>
-    <workbookView xWindow="915" yWindow="915" windowWidth="25995" windowHeight="14280" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Goals and Instructions" sheetId="7" r:id="rId1"/>
@@ -41,6 +41,24 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={49538CE4-14DD-426F-986D-258C246FA2AD}</author>
+  </authors>
+  <commentList>
+    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{49538CE4-14DD-426F-986D-258C246FA2AD}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    https://youtu.be/v9yHmosJURk</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
@@ -399,7 +417,7 @@
     <numFmt numFmtId="164" formatCode="0.0000000%"/>
     <numFmt numFmtId="165" formatCode="0.00000%"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -499,15 +517,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <u/>
-      <sz val="14"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -518,6 +527,20 @@
       <sz val="10"/>
       <color theme="0"/>
       <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="12">
@@ -809,7 +832,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -934,6 +957,63 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -960,9 +1040,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -984,62 +1061,23 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1160,6 +1198,12 @@
     <xdr:clientData/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Richard Ketchersid" id="{9F5C1CFB-46E6-4089-BB1B-089ADA43D36F}" userId="S::richard.ketchersid@gcu.edu::a14ec2f7-27bd-40c3-90d9-209834cdef57" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1423,8 +1467,22 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="D8" dT="2026-07-16T20:19:58.71" personId="{9F5C1CFB-46E6-4089-BB1B-089ADA43D36F}" id="{49538CE4-14DD-426F-986D-258C246FA2AD}">
+    <text>https://youtu.be/v9yHmosJURk</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>2595144275</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="28" url="https://youtu.be/v9yHmosJURk"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4C49091-89C4-4C81-92DE-E00831BDB54A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4C49091-89C4-4C81-92DE-E00831BDB54A}">
   <dimension ref="B1:I9"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
@@ -1436,87 +1494,92 @@
       <c r="B2" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="42"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="59"/>
     </row>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="43"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="45"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="62"/>
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="43"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="45"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="62"/>
     </row>
     <row r="5" spans="2:9" ht="16.5" thickBot="1">
       <c r="B5" s="38"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="45"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="62"/>
     </row>
     <row r="6" spans="2:9" ht="16.5" thickBot="1">
       <c r="B6" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="46"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="47"/>
-      <c r="I6" s="48"/>
-    </row>
-    <row r="7" spans="2:9" ht="31.5">
+      <c r="D6" s="63"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="65"/>
+    </row>
+    <row r="7" spans="2:9" ht="32.25" thickBot="1">
       <c r="B7" s="39" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="18.75">
+    <row r="8" spans="2:9" ht="18.75" customHeight="1">
       <c r="B8" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="49" t="s">
+      <c r="D8" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-    </row>
-    <row r="9" spans="2:9">
+      <c r="E8" s="73"/>
+      <c r="F8" s="73"/>
+      <c r="G8" s="74"/>
+    </row>
+    <row r="9" spans="2:9" ht="16.5" thickBot="1">
       <c r="B9" s="38" t="s">
         <v>8</v>
       </c>
+      <c r="D9" s="75"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="D2:I6"/>
-    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="D8:G9"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D8:G8" r:id="rId1" display="Video on counting" xr:uid="{B27F1C40-E169-44D2-8209-6BC6A7A5ECFE}"/>
+    <hyperlink ref="D8:G9" r:id="rId1" display="Video on counting" xr:uid="{BD97EEB3-2AAF-4125-BE9F-2D5C4AD979C5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1550,7 +1613,7 @@
       <c r="B2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="71" t="s">
+      <c r="C2" s="55" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="28"/>
@@ -1565,15 +1628,15 @@
     </row>
     <row r="4" spans="1:9" ht="16.5" thickBot="1">
       <c r="A4" s="28"/>
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="51"/>
+      <c r="C4" s="67"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
     </row>
     <row r="5" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="68" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="13" t="s">
@@ -1586,7 +1649,7 @@
       <c r="E5" s="28"/>
     </row>
     <row r="6" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A6" s="53"/>
+      <c r="A6" s="69"/>
       <c r="B6" s="15" t="s">
         <v>15</v>
       </c>
@@ -1598,7 +1661,7 @@
       <c r="F6" s="24"/>
     </row>
     <row r="7" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A7" s="54"/>
+      <c r="A7" s="70"/>
       <c r="B7" s="17" t="s">
         <v>17</v>
       </c>
@@ -1700,92 +1763,92 @@
         <f ca="1">(1-G13)/G13</f>
         <v>1189</v>
       </c>
-      <c r="I13" s="72" t="str">
+      <c r="I13" s="56" t="str">
         <f ca="1">"Your odds of winning are 1 to "&amp;H13&amp;"!"</f>
         <v>Your odds of winning are 1 to 1189!</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="70.5" customHeight="1">
-      <c r="A14" s="70" t="str" cm="1">
+      <c r="A14" s="54" t="str" cm="1">
         <f t="array" aca="1" ref="A14" ca="1">IF(C$2="Your Name Here", "Enter your name in C2",INDIRECT("Sheet3!A"&amp;Random!I19))</f>
         <v>Enter your name in C2</v>
       </c>
-      <c r="B14" s="61"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="72" t="str">
+      <c r="B14" s="45"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="50"/>
+      <c r="I14" s="56" t="str">
         <f>"Your odds of winning are 1 to "&amp;IF(NOT(ISBLANK(H14)),ROUND(H14,0),"???")&amp;"!"</f>
         <v>Your odds of winning are 1 to ???!</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="70.5" customHeight="1">
-      <c r="A15" s="70" t="str" cm="1">
+      <c r="A15" s="54" t="str" cm="1">
         <f t="array" aca="1" ref="A15" ca="1">IF(C$2="Your Name Here", "Enter your name in C2",INDIRECT("Sheet3!A"&amp;Random!I20))</f>
         <v>Enter your name in C2</v>
       </c>
-      <c r="B15" s="61"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="63"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="65"/>
-      <c r="H15" s="66"/>
-      <c r="I15" s="72" t="str">
+      <c r="B15" s="45"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="56" t="str">
         <f t="shared" ref="I15:I18" si="0">"Your odds of winning are 1 to "&amp;IF(NOT(ISBLANK(H15)),ROUND(H15,0),"???")&amp;"!"</f>
         <v>Your odds of winning are 1 to ???!</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="70.5" customHeight="1">
-      <c r="A16" s="70" t="str" cm="1">
+      <c r="A16" s="54" t="str" cm="1">
         <f t="array" aca="1" ref="A16" ca="1">IF(C$2="Your Name Here", "Enter your name in C2",INDIRECT("Sheet3!A"&amp;Random!I21))</f>
         <v>Enter your name in C2</v>
       </c>
-      <c r="B16" s="67"/>
-      <c r="C16" s="68"/>
-      <c r="D16" s="69"/>
-      <c r="E16" s="68"/>
-      <c r="F16" s="64"/>
-      <c r="G16" s="65"/>
-      <c r="H16" s="66"/>
-      <c r="I16" s="72" t="str">
+      <c r="B16" s="51"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="50"/>
+      <c r="I16" s="56" t="str">
         <f t="shared" si="0"/>
         <v>Your odds of winning are 1 to ???!</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="70.5" customHeight="1">
-      <c r="A17" s="70" t="str" cm="1">
+      <c r="A17" s="54" t="str" cm="1">
         <f t="array" aca="1" ref="A17" ca="1">IF(C$2="Your Name Here", "Enter your name in C2",INDIRECT("Sheet3!A"&amp;Random!I22))</f>
         <v>Enter your name in C2</v>
       </c>
-      <c r="B17" s="67"/>
-      <c r="C17" s="68"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="64"/>
-      <c r="G17" s="65"/>
-      <c r="H17" s="66"/>
-      <c r="I17" s="72" t="str">
+      <c r="B17" s="51"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="49"/>
+      <c r="H17" s="50"/>
+      <c r="I17" s="56" t="str">
         <f t="shared" si="0"/>
         <v>Your odds of winning are 1 to ???!</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="70.5" customHeight="1">
-      <c r="A18" s="70" t="str" cm="1">
+      <c r="A18" s="54" t="str" cm="1">
         <f t="array" aca="1" ref="A18" ca="1">IF(C$2="Your Name Here", "Enter your name in C2",INDIRECT("Sheet3!A"&amp;Random!I23))</f>
         <v>Enter your name in C2</v>
       </c>
-      <c r="B18" s="61"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="64"/>
-      <c r="G18" s="65"/>
-      <c r="H18" s="66"/>
-      <c r="I18" s="72" t="str">
+      <c r="B18" s="45"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="49"/>
+      <c r="H18" s="50"/>
+      <c r="I18" s="56" t="str">
         <f t="shared" si="0"/>
         <v>Your odds of winning are 1 to ???!</v>
       </c>
@@ -2013,15 +2076,15 @@
     </row>
     <row r="4" spans="1:9" ht="16.5" thickBot="1">
       <c r="A4" s="28"/>
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="51"/>
+      <c r="C4" s="67"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
     </row>
     <row r="5" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="68" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="13" t="s">
@@ -2034,7 +2097,7 @@
       <c r="E5" s="28"/>
     </row>
     <row r="6" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A6" s="53"/>
+      <c r="A6" s="69"/>
       <c r="B6" s="15" t="s">
         <v>15</v>
       </c>
@@ -2046,7 +2109,7 @@
       <c r="F6" s="24"/>
     </row>
     <row r="7" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A7" s="54"/>
+      <c r="A7" s="70"/>
       <c r="B7" s="17" t="s">
         <v>17</v>
       </c>
@@ -2453,2022 +2516,2022 @@
   <dimension ref="A1:W55"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="4" width="9.125" style="56" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="56" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.875" style="56" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.125" style="56" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="56" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.375" style="56" bestFit="1" customWidth="1"/>
-    <col min="10" max="23" width="9.125" style="56" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9" style="56"/>
+    <col min="1" max="4" width="9.125" style="40" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="40" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.875" style="40" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.125" style="40" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="40" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.375" style="40" bestFit="1" customWidth="1"/>
+    <col min="10" max="23" width="9.125" style="40" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9" style="40"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
-      <c r="H1" s="56">
+      <c r="H1" s="40">
         <v>1</v>
       </c>
-      <c r="I1" s="56">
+      <c r="I1" s="40">
         <v>2</v>
       </c>
-      <c r="J1" s="56">
+      <c r="J1" s="40">
         <v>3</v>
       </c>
-      <c r="K1" s="56">
+      <c r="K1" s="40">
         <v>4</v>
       </c>
-      <c r="L1" s="56">
+      <c r="L1" s="40">
         <v>5</v>
       </c>
-      <c r="M1" s="56">
+      <c r="M1" s="40">
         <v>6</v>
       </c>
-      <c r="N1" s="56">
+      <c r="N1" s="40">
         <v>7</v>
       </c>
-      <c r="O1" s="56">
+      <c r="O1" s="40">
         <v>8</v>
       </c>
-      <c r="P1" s="56">
+      <c r="P1" s="40">
         <v>9</v>
       </c>
-      <c r="Q1" s="56">
+      <c r="Q1" s="40">
         <v>10</v>
       </c>
-      <c r="R1" s="56">
+      <c r="R1" s="40">
         <v>11</v>
       </c>
-      <c r="S1" s="56">
+      <c r="S1" s="40">
         <v>12</v>
       </c>
-      <c r="T1" s="56">
+      <c r="T1" s="40">
         <v>13</v>
       </c>
-      <c r="U1" s="56">
+      <c r="U1" s="40">
         <v>14</v>
       </c>
-      <c r="V1" s="56">
+      <c r="V1" s="40">
         <v>15</v>
       </c>
-      <c r="W1" s="56">
+      <c r="W1" s="40">
         <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:23">
-      <c r="G2" s="56">
+      <c r="G2" s="40">
         <v>1</v>
       </c>
-      <c r="H2" s="56">
+      <c r="H2" s="40">
         <v>2</v>
       </c>
-      <c r="I2" s="56">
+      <c r="I2" s="40">
         <v>3</v>
       </c>
-      <c r="J2" s="56">
+      <c r="J2" s="40">
         <v>5</v>
       </c>
-      <c r="K2" s="56">
+      <c r="K2" s="40">
         <v>7</v>
       </c>
-      <c r="L2" s="56">
+      <c r="L2" s="40">
         <v>11</v>
       </c>
-      <c r="M2" s="56">
+      <c r="M2" s="40">
         <v>13</v>
       </c>
-      <c r="N2" s="56">
+      <c r="N2" s="40">
         <v>17</v>
       </c>
-      <c r="O2" s="56">
+      <c r="O2" s="40">
         <v>19</v>
       </c>
-      <c r="P2" s="56">
+      <c r="P2" s="40">
         <v>23</v>
       </c>
-      <c r="Q2" s="56">
+      <c r="Q2" s="40">
         <v>29</v>
       </c>
-      <c r="R2" s="56">
+      <c r="R2" s="40">
         <v>947</v>
       </c>
-      <c r="S2" s="56">
+      <c r="S2" s="40">
         <v>953</v>
       </c>
-      <c r="T2" s="56">
+      <c r="T2" s="40">
         <v>967</v>
       </c>
-      <c r="U2" s="56">
+      <c r="U2" s="40">
         <v>971</v>
       </c>
-      <c r="V2" s="56">
+      <c r="V2" s="40">
         <v>977</v>
       </c>
-      <c r="W2" s="56">
+      <c r="W2" s="40">
         <v>983</v>
       </c>
     </row>
     <row r="3" spans="1:23">
-      <c r="G3" s="56">
+      <c r="G3" s="40">
         <v>2</v>
       </c>
-      <c r="H3" s="56">
+      <c r="H3" s="40">
         <v>31</v>
       </c>
-      <c r="I3" s="56">
+      <c r="I3" s="40">
         <v>37</v>
       </c>
-      <c r="J3" s="56">
+      <c r="J3" s="40">
         <v>41</v>
       </c>
-      <c r="K3" s="56">
+      <c r="K3" s="40">
         <v>43</v>
       </c>
-      <c r="L3" s="56">
+      <c r="L3" s="40">
         <v>47</v>
       </c>
-      <c r="M3" s="56">
+      <c r="M3" s="40">
         <v>53</v>
       </c>
-      <c r="N3" s="56">
+      <c r="N3" s="40">
         <v>59</v>
       </c>
-      <c r="O3" s="56">
+      <c r="O3" s="40">
         <v>61</v>
       </c>
-      <c r="P3" s="56">
+      <c r="P3" s="40">
         <v>67</v>
       </c>
-      <c r="Q3" s="56">
+      <c r="Q3" s="40">
         <v>71</v>
       </c>
-      <c r="R3" s="56">
+      <c r="R3" s="40">
         <v>991</v>
       </c>
-      <c r="S3" s="56">
+      <c r="S3" s="40">
         <v>997</v>
       </c>
-      <c r="T3" s="56">
+      <c r="T3" s="40">
         <v>1009</v>
       </c>
-      <c r="U3" s="56">
+      <c r="U3" s="40">
         <v>1013</v>
       </c>
-      <c r="V3" s="56">
+      <c r="V3" s="40">
         <v>1019</v>
       </c>
-      <c r="W3" s="56">
+      <c r="W3" s="40">
         <v>1021</v>
       </c>
     </row>
     <row r="4" spans="1:23">
-      <c r="G4" s="56">
+      <c r="G4" s="40">
         <v>3</v>
       </c>
-      <c r="H4" s="56">
+      <c r="H4" s="40">
         <v>73</v>
       </c>
-      <c r="I4" s="56">
+      <c r="I4" s="40">
         <v>79</v>
       </c>
-      <c r="J4" s="56">
+      <c r="J4" s="40">
         <v>83</v>
       </c>
-      <c r="K4" s="56">
+      <c r="K4" s="40">
         <v>89</v>
       </c>
-      <c r="L4" s="56">
+      <c r="L4" s="40">
         <v>97</v>
       </c>
-      <c r="M4" s="56">
+      <c r="M4" s="40">
         <v>101</v>
       </c>
-      <c r="N4" s="56">
+      <c r="N4" s="40">
         <v>103</v>
       </c>
-      <c r="O4" s="56">
+      <c r="O4" s="40">
         <v>107</v>
       </c>
-      <c r="P4" s="56">
+      <c r="P4" s="40">
         <v>109</v>
       </c>
-      <c r="Q4" s="56">
+      <c r="Q4" s="40">
         <v>113</v>
       </c>
-      <c r="R4" s="56">
+      <c r="R4" s="40">
         <v>1031</v>
       </c>
-      <c r="S4" s="56">
+      <c r="S4" s="40">
         <v>1033</v>
       </c>
-      <c r="T4" s="56">
+      <c r="T4" s="40">
         <v>1039</v>
       </c>
-      <c r="U4" s="56">
+      <c r="U4" s="40">
         <v>1049</v>
       </c>
-      <c r="V4" s="56">
+      <c r="V4" s="40">
         <v>1051</v>
       </c>
-      <c r="W4" s="56">
+      <c r="W4" s="40">
         <v>1061</v>
       </c>
     </row>
     <row r="5" spans="1:23">
-      <c r="G5" s="56">
+      <c r="G5" s="40">
         <v>4</v>
       </c>
-      <c r="H5" s="56">
+      <c r="H5" s="40">
         <v>127</v>
       </c>
-      <c r="I5" s="56">
+      <c r="I5" s="40">
         <v>131</v>
       </c>
-      <c r="J5" s="56">
+      <c r="J5" s="40">
         <v>137</v>
       </c>
-      <c r="K5" s="56">
+      <c r="K5" s="40">
         <v>139</v>
       </c>
-      <c r="L5" s="56">
+      <c r="L5" s="40">
         <v>149</v>
       </c>
-      <c r="M5" s="56">
+      <c r="M5" s="40">
         <v>151</v>
       </c>
-      <c r="N5" s="56">
+      <c r="N5" s="40">
         <v>157</v>
       </c>
-      <c r="O5" s="56">
+      <c r="O5" s="40">
         <v>163</v>
       </c>
-      <c r="P5" s="56">
+      <c r="P5" s="40">
         <v>167</v>
       </c>
-      <c r="Q5" s="56">
+      <c r="Q5" s="40">
         <v>173</v>
       </c>
-      <c r="R5" s="56">
+      <c r="R5" s="40">
         <v>1993</v>
       </c>
-      <c r="S5" s="56">
+      <c r="S5" s="40">
         <v>1997</v>
       </c>
-      <c r="T5" s="56">
+      <c r="T5" s="40">
         <v>1999</v>
       </c>
-      <c r="U5" s="56">
+      <c r="U5" s="40">
         <v>2003</v>
       </c>
-      <c r="V5" s="56">
+      <c r="V5" s="40">
         <v>2011</v>
       </c>
-      <c r="W5" s="56">
+      <c r="W5" s="40">
         <v>2017</v>
       </c>
     </row>
     <row r="6" spans="1:23">
-      <c r="A6" s="56">
+      <c r="A6" s="40">
         <v>1</v>
       </c>
-      <c r="B6" s="56">
+      <c r="B6" s="40">
         <f>CODE(MID(Games!C$2,A6,1))</f>
         <v>89</v>
       </c>
-      <c r="C6" s="56">
+      <c r="C6" s="40">
         <f>MOD(B6,16)</f>
         <v>9</v>
       </c>
-      <c r="D6" s="56">
+      <c r="D6" s="40">
         <f>MOD((B6-C6)/16,16)</f>
         <v>5</v>
       </c>
-      <c r="E6" s="56">
+      <c r="E6" s="40">
         <f ca="1">INDIRECT("R"&amp;(C6+1)&amp;"C"&amp;(D6+7),0)</f>
         <v>439</v>
       </c>
-      <c r="G6" s="56">
+      <c r="G6" s="40">
         <v>5</v>
       </c>
-      <c r="H6" s="56">
+      <c r="H6" s="40">
         <v>179</v>
       </c>
-      <c r="I6" s="56">
+      <c r="I6" s="40">
         <v>181</v>
       </c>
-      <c r="J6" s="56">
+      <c r="J6" s="40">
         <v>191</v>
       </c>
-      <c r="K6" s="56">
+      <c r="K6" s="40">
         <v>193</v>
       </c>
-      <c r="L6" s="56">
+      <c r="L6" s="40">
         <v>197</v>
       </c>
-      <c r="M6" s="56">
+      <c r="M6" s="40">
         <v>199</v>
       </c>
-      <c r="N6" s="56">
+      <c r="N6" s="40">
         <v>211</v>
       </c>
-      <c r="O6" s="56">
+      <c r="O6" s="40">
         <v>223</v>
       </c>
-      <c r="P6" s="56">
+      <c r="P6" s="40">
         <v>227</v>
       </c>
-      <c r="Q6" s="56">
+      <c r="Q6" s="40">
         <v>229</v>
       </c>
-      <c r="R6" s="56">
+      <c r="R6" s="40">
         <v>2063</v>
       </c>
-      <c r="S6" s="56">
+      <c r="S6" s="40">
         <v>2069</v>
       </c>
-      <c r="T6" s="56">
+      <c r="T6" s="40">
         <v>2081</v>
       </c>
-      <c r="U6" s="56">
+      <c r="U6" s="40">
         <v>2083</v>
       </c>
-      <c r="V6" s="56">
+      <c r="V6" s="40">
         <v>2087</v>
       </c>
-      <c r="W6" s="56">
+      <c r="W6" s="40">
         <v>2089</v>
       </c>
     </row>
     <row r="7" spans="1:23">
-      <c r="A7" s="56">
+      <c r="A7" s="40">
         <v>2</v>
       </c>
-      <c r="B7" s="56">
+      <c r="B7" s="40">
         <f>CODE(MID(Games!C$2,A7,1))</f>
         <v>111</v>
       </c>
-      <c r="C7" s="56">
+      <c r="C7" s="40">
         <f t="shared" ref="C7:C10" si="0">MOD(B7,16)</f>
         <v>15</v>
       </c>
-      <c r="D7" s="56">
+      <c r="D7" s="40">
         <f t="shared" ref="D7:D10" si="1">MOD((B7-C7)/16,16)</f>
         <v>6</v>
       </c>
-      <c r="E7" s="56">
+      <c r="E7" s="40">
         <f t="shared" ref="E7:E10" ca="1" si="2">INDIRECT("R"&amp;(C7+1)&amp;"C"&amp;(D7+7),0)</f>
         <v>839</v>
       </c>
-      <c r="G7" s="56">
+      <c r="G7" s="40">
         <v>6</v>
       </c>
-      <c r="H7" s="56">
+      <c r="H7" s="40">
         <v>233</v>
       </c>
-      <c r="I7" s="56">
+      <c r="I7" s="40">
         <v>239</v>
       </c>
-      <c r="J7" s="56">
+      <c r="J7" s="40">
         <v>241</v>
       </c>
-      <c r="K7" s="56">
+      <c r="K7" s="40">
         <v>251</v>
       </c>
-      <c r="L7" s="56">
+      <c r="L7" s="40">
         <v>257</v>
       </c>
-      <c r="M7" s="56">
+      <c r="M7" s="40">
         <v>263</v>
       </c>
-      <c r="N7" s="56">
+      <c r="N7" s="40">
         <v>269</v>
       </c>
-      <c r="O7" s="56">
+      <c r="O7" s="40">
         <v>271</v>
       </c>
-      <c r="P7" s="56">
+      <c r="P7" s="40">
         <v>277</v>
       </c>
-      <c r="Q7" s="56">
+      <c r="Q7" s="40">
         <v>281</v>
       </c>
-      <c r="R7" s="56">
+      <c r="R7" s="40">
         <v>2131</v>
       </c>
-      <c r="S7" s="56">
+      <c r="S7" s="40">
         <v>2137</v>
       </c>
-      <c r="T7" s="56">
+      <c r="T7" s="40">
         <v>2141</v>
       </c>
-      <c r="U7" s="56">
+      <c r="U7" s="40">
         <v>2143</v>
       </c>
-      <c r="V7" s="56">
+      <c r="V7" s="40">
         <v>2153</v>
       </c>
-      <c r="W7" s="56">
+      <c r="W7" s="40">
         <v>2161</v>
       </c>
     </row>
     <row r="8" spans="1:23">
-      <c r="A8" s="56">
+      <c r="A8" s="40">
         <v>3</v>
       </c>
-      <c r="B8" s="56">
+      <c r="B8" s="40">
         <f>CODE(MID(Games!C$2,A8,1))</f>
         <v>117</v>
       </c>
-      <c r="C8" s="56">
+      <c r="C8" s="40">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="D8" s="56">
+      <c r="D8" s="40">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="E8" s="56">
+      <c r="E8" s="40">
         <f t="shared" ca="1" si="2"/>
         <v>211</v>
       </c>
-      <c r="G8" s="56">
+      <c r="G8" s="40">
         <v>7</v>
       </c>
-      <c r="H8" s="56">
+      <c r="H8" s="40">
         <v>283</v>
       </c>
-      <c r="I8" s="56">
+      <c r="I8" s="40">
         <v>293</v>
       </c>
-      <c r="J8" s="56">
+      <c r="J8" s="40">
         <v>307</v>
       </c>
-      <c r="K8" s="56">
+      <c r="K8" s="40">
         <v>311</v>
       </c>
-      <c r="L8" s="56">
+      <c r="L8" s="40">
         <v>313</v>
       </c>
-      <c r="M8" s="56">
+      <c r="M8" s="40">
         <v>317</v>
       </c>
-      <c r="N8" s="56">
+      <c r="N8" s="40">
         <v>331</v>
       </c>
-      <c r="O8" s="56">
+      <c r="O8" s="40">
         <v>337</v>
       </c>
-      <c r="P8" s="56">
+      <c r="P8" s="40">
         <v>347</v>
       </c>
-      <c r="Q8" s="56">
+      <c r="Q8" s="40">
         <v>349</v>
       </c>
-      <c r="R8" s="56">
+      <c r="R8" s="40">
         <v>2221</v>
       </c>
-      <c r="S8" s="56">
+      <c r="S8" s="40">
         <v>2237</v>
       </c>
-      <c r="T8" s="56">
+      <c r="T8" s="40">
         <v>2239</v>
       </c>
-      <c r="U8" s="56">
+      <c r="U8" s="40">
         <v>2243</v>
       </c>
-      <c r="V8" s="56">
+      <c r="V8" s="40">
         <v>2251</v>
       </c>
-      <c r="W8" s="56">
+      <c r="W8" s="40">
         <v>2267</v>
       </c>
     </row>
     <row r="9" spans="1:23">
-      <c r="A9" s="56">
+      <c r="A9" s="40">
         <v>4</v>
       </c>
-      <c r="B9" s="56">
+      <c r="B9" s="40">
         <f>CODE(MID(Games!C$2,A9,1))</f>
         <v>114</v>
       </c>
-      <c r="C9" s="56">
+      <c r="C9" s="40">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D9" s="56">
+      <c r="D9" s="40">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="E9" s="56">
+      <c r="E9" s="40">
         <f t="shared" ca="1" si="2"/>
         <v>59</v>
       </c>
-      <c r="G9" s="56">
+      <c r="G9" s="40">
         <v>8</v>
       </c>
-      <c r="H9" s="56">
+      <c r="H9" s="40">
         <v>353</v>
       </c>
-      <c r="I9" s="56">
+      <c r="I9" s="40">
         <v>359</v>
       </c>
-      <c r="J9" s="56">
+      <c r="J9" s="40">
         <v>367</v>
       </c>
-      <c r="K9" s="56">
+      <c r="K9" s="40">
         <v>373</v>
       </c>
-      <c r="L9" s="56">
+      <c r="L9" s="40">
         <v>379</v>
       </c>
-      <c r="M9" s="56">
+      <c r="M9" s="40">
         <v>383</v>
       </c>
-      <c r="N9" s="56">
+      <c r="N9" s="40">
         <v>389</v>
       </c>
-      <c r="O9" s="56">
+      <c r="O9" s="40">
         <v>397</v>
       </c>
-      <c r="P9" s="56">
+      <c r="P9" s="40">
         <v>401</v>
       </c>
-      <c r="Q9" s="56">
+      <c r="Q9" s="40">
         <v>409</v>
       </c>
-      <c r="R9" s="56">
+      <c r="R9" s="40">
         <v>2293</v>
       </c>
-      <c r="S9" s="56">
+      <c r="S9" s="40">
         <v>2297</v>
       </c>
-      <c r="T9" s="56">
+      <c r="T9" s="40">
         <v>2309</v>
       </c>
-      <c r="U9" s="56">
+      <c r="U9" s="40">
         <v>2311</v>
       </c>
-      <c r="V9" s="56">
+      <c r="V9" s="40">
         <v>2333</v>
       </c>
-      <c r="W9" s="56">
+      <c r="W9" s="40">
         <v>2339</v>
       </c>
     </row>
     <row r="10" spans="1:23">
-      <c r="A10" s="56">
+      <c r="A10" s="40">
         <v>5</v>
       </c>
-      <c r="B10" s="56">
+      <c r="B10" s="40">
         <f>CODE(MID(Games!C$2,A10,1))</f>
         <v>32</v>
       </c>
-      <c r="C10" s="56">
+      <c r="C10" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D10" s="56">
+      <c r="D10" s="40">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="E10" s="56">
+      <c r="E10" s="40">
         <f t="shared" ca="1" si="2"/>
         <v>2</v>
       </c>
-      <c r="G10" s="56">
+      <c r="G10" s="40">
         <v>9</v>
       </c>
-      <c r="H10" s="56">
+      <c r="H10" s="40">
         <v>419</v>
       </c>
-      <c r="I10" s="56">
+      <c r="I10" s="40">
         <v>421</v>
       </c>
-      <c r="J10" s="56">
+      <c r="J10" s="40">
         <v>431</v>
       </c>
-      <c r="K10" s="56">
+      <c r="K10" s="40">
         <v>433</v>
       </c>
-      <c r="L10" s="56">
+      <c r="L10" s="40">
         <v>439</v>
       </c>
-      <c r="M10" s="56">
+      <c r="M10" s="40">
         <v>443</v>
       </c>
-      <c r="N10" s="56">
+      <c r="N10" s="40">
         <v>449</v>
       </c>
-      <c r="O10" s="56">
+      <c r="O10" s="40">
         <v>457</v>
       </c>
-      <c r="P10" s="56">
+      <c r="P10" s="40">
         <v>461</v>
       </c>
-      <c r="Q10" s="56">
+      <c r="Q10" s="40">
         <v>463</v>
       </c>
-      <c r="R10" s="56">
+      <c r="R10" s="40">
         <v>2371</v>
       </c>
-      <c r="S10" s="56">
+      <c r="S10" s="40">
         <v>2377</v>
       </c>
-      <c r="T10" s="56">
+      <c r="T10" s="40">
         <v>2381</v>
       </c>
-      <c r="U10" s="56">
+      <c r="U10" s="40">
         <v>2383</v>
       </c>
-      <c r="V10" s="56">
+      <c r="V10" s="40">
         <v>2389</v>
       </c>
-      <c r="W10" s="56">
+      <c r="W10" s="40">
         <v>2393</v>
       </c>
     </row>
     <row r="11" spans="1:23">
-      <c r="A11" s="56" t="s">
+      <c r="A11" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="56">
+      <c r="B11" s="40">
         <f ca="1">MOD(PRODUCT(E6:E10),F13)</f>
         <v>3778</v>
       </c>
-      <c r="F11" s="56">
+      <c r="F11" s="40">
         <v>1103515245</v>
       </c>
-      <c r="G11" s="56">
+      <c r="G11" s="40">
         <v>10</v>
       </c>
-      <c r="H11" s="56">
+      <c r="H11" s="40">
         <v>467</v>
       </c>
-      <c r="I11" s="56">
+      <c r="I11" s="40">
         <v>479</v>
       </c>
-      <c r="J11" s="56">
+      <c r="J11" s="40">
         <v>487</v>
       </c>
-      <c r="K11" s="56">
+      <c r="K11" s="40">
         <v>491</v>
       </c>
-      <c r="L11" s="56">
+      <c r="L11" s="40">
         <v>499</v>
       </c>
-      <c r="M11" s="56">
+      <c r="M11" s="40">
         <v>503</v>
       </c>
-      <c r="N11" s="56">
+      <c r="N11" s="40">
         <v>509</v>
       </c>
-      <c r="O11" s="56">
+      <c r="O11" s="40">
         <v>521</v>
       </c>
-      <c r="P11" s="56">
+      <c r="P11" s="40">
         <v>523</v>
       </c>
-      <c r="Q11" s="56">
+      <c r="Q11" s="40">
         <v>541</v>
       </c>
-      <c r="R11" s="56">
+      <c r="R11" s="40">
         <v>2437</v>
       </c>
-      <c r="S11" s="56">
+      <c r="S11" s="40">
         <v>2441</v>
       </c>
-      <c r="T11" s="56">
+      <c r="T11" s="40">
         <v>2447</v>
       </c>
-      <c r="U11" s="56">
+      <c r="U11" s="40">
         <v>2459</v>
       </c>
-      <c r="V11" s="56">
+      <c r="V11" s="40">
         <v>2467</v>
       </c>
-      <c r="W11" s="56">
+      <c r="W11" s="40">
         <v>2473</v>
       </c>
     </row>
     <row r="12" spans="1:23">
-      <c r="A12" s="56" t="s">
+      <c r="A12" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="56">
+      <c r="B12" s="40">
         <f ca="1">MOD(B11*F11+F12,F13)</f>
         <v>5331</v>
       </c>
-      <c r="C12" s="56">
+      <c r="C12" s="40">
         <f ca="1">MOD(B12,2)</f>
         <v>1</v>
       </c>
-      <c r="D12" s="56">
+      <c r="D12" s="40">
         <f ca="1">B12/F$13</f>
         <v>0.162689208984375</v>
       </c>
-      <c r="E12" s="56">
+      <c r="E12" s="40">
         <f ca="1">IF(D12&lt;0.25,0,IF(D12&lt;0.5,1,IF(D12&lt;0.75,3,4)))</f>
         <v>0</v>
       </c>
-      <c r="F12" s="56">
+      <c r="F12" s="40">
         <v>12345</v>
       </c>
-      <c r="G12" s="56">
+      <c r="G12" s="40">
         <v>11</v>
       </c>
-      <c r="H12" s="56">
+      <c r="H12" s="40">
         <v>547</v>
       </c>
-      <c r="I12" s="56">
+      <c r="I12" s="40">
         <v>557</v>
       </c>
-      <c r="J12" s="56">
+      <c r="J12" s="40">
         <v>563</v>
       </c>
-      <c r="K12" s="56">
+      <c r="K12" s="40">
         <v>569</v>
       </c>
-      <c r="L12" s="56">
+      <c r="L12" s="40">
         <v>571</v>
       </c>
-      <c r="M12" s="56">
+      <c r="M12" s="40">
         <v>577</v>
       </c>
-      <c r="N12" s="56">
+      <c r="N12" s="40">
         <v>587</v>
       </c>
-      <c r="O12" s="56">
+      <c r="O12" s="40">
         <v>593</v>
       </c>
-      <c r="P12" s="56">
+      <c r="P12" s="40">
         <v>599</v>
       </c>
-      <c r="Q12" s="56">
+      <c r="Q12" s="40">
         <v>601</v>
       </c>
-      <c r="R12" s="56">
+      <c r="R12" s="40">
         <v>2539</v>
       </c>
-      <c r="S12" s="56">
+      <c r="S12" s="40">
         <v>2543</v>
       </c>
-      <c r="T12" s="56">
+      <c r="T12" s="40">
         <v>2549</v>
       </c>
-      <c r="U12" s="56">
+      <c r="U12" s="40">
         <v>2551</v>
       </c>
-      <c r="V12" s="56">
+      <c r="V12" s="40">
         <v>2557</v>
       </c>
-      <c r="W12" s="56">
+      <c r="W12" s="40">
         <v>2579</v>
       </c>
     </row>
     <row r="13" spans="1:23">
-      <c r="A13" s="56" t="s">
+      <c r="A13" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="57">
+      <c r="B13" s="41">
         <f t="shared" ref="B13:B55" ca="1" si="3">MOD(B12*F$11+F$12,F$13)</f>
         <v>22544</v>
       </c>
-      <c r="C13" s="56">
+      <c r="C13" s="40">
         <f t="shared" ref="C13:C55" ca="1" si="4">IF(D13&lt;0.5,0,1)</f>
         <v>1</v>
       </c>
-      <c r="D13" s="56">
+      <c r="D13" s="40">
         <f t="shared" ref="D13:D55" ca="1" si="5">B13/F$13</f>
         <v>0.68798828125</v>
       </c>
-      <c r="E13" s="56">
+      <c r="E13" s="40">
         <f t="shared" ref="E13:E55" ca="1" si="6">IF(D13&lt;0.25,0,IF(D13&lt;0.5,1,IF(D13&lt;0.75,3,4)))</f>
         <v>3</v>
       </c>
-      <c r="F13" s="56">
+      <c r="F13" s="40">
         <v>32768</v>
       </c>
-      <c r="G13" s="56">
+      <c r="G13" s="40">
         <v>12</v>
       </c>
-      <c r="H13" s="56">
+      <c r="H13" s="40">
         <v>607</v>
       </c>
-      <c r="I13" s="56">
+      <c r="I13" s="40">
         <v>613</v>
       </c>
-      <c r="J13" s="56">
+      <c r="J13" s="40">
         <v>617</v>
       </c>
-      <c r="K13" s="56">
+      <c r="K13" s="40">
         <v>619</v>
       </c>
-      <c r="L13" s="56">
+      <c r="L13" s="40">
         <v>631</v>
       </c>
-      <c r="M13" s="56">
+      <c r="M13" s="40">
         <v>641</v>
       </c>
-      <c r="N13" s="56">
+      <c r="N13" s="40">
         <v>643</v>
       </c>
-      <c r="O13" s="56">
+      <c r="O13" s="40">
         <v>647</v>
       </c>
-      <c r="P13" s="56">
+      <c r="P13" s="40">
         <v>653</v>
       </c>
-      <c r="Q13" s="56">
+      <c r="Q13" s="40">
         <v>659</v>
       </c>
-      <c r="R13" s="56">
+      <c r="R13" s="40">
         <v>2621</v>
       </c>
-      <c r="S13" s="56">
+      <c r="S13" s="40">
         <v>2633</v>
       </c>
-      <c r="T13" s="56">
+      <c r="T13" s="40">
         <v>2647</v>
       </c>
-      <c r="U13" s="56">
+      <c r="U13" s="40">
         <v>2657</v>
       </c>
-      <c r="V13" s="56">
+      <c r="V13" s="40">
         <v>2659</v>
       </c>
-      <c r="W13" s="56">
+      <c r="W13" s="40">
         <v>2663</v>
       </c>
     </row>
     <row r="14" spans="1:23">
-      <c r="A14" s="56" t="s">
+      <c r="A14" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="57">
+      <c r="B14" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>3849</v>
       </c>
-      <c r="C14" s="56">
+      <c r="C14" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D14" s="56">
+      <c r="D14" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.117462158203125</v>
       </c>
-      <c r="E14" s="56">
+      <c r="E14" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="G14" s="56">
+      <c r="G14" s="40">
         <v>13</v>
       </c>
-      <c r="H14" s="56">
+      <c r="H14" s="40">
         <v>661</v>
       </c>
-      <c r="I14" s="56">
+      <c r="I14" s="40">
         <v>673</v>
       </c>
-      <c r="J14" s="56">
+      <c r="J14" s="40">
         <v>677</v>
       </c>
-      <c r="K14" s="56">
+      <c r="K14" s="40">
         <v>683</v>
       </c>
-      <c r="L14" s="56">
+      <c r="L14" s="40">
         <v>691</v>
       </c>
-      <c r="M14" s="56">
+      <c r="M14" s="40">
         <v>701</v>
       </c>
-      <c r="N14" s="56">
+      <c r="N14" s="40">
         <v>709</v>
       </c>
-      <c r="O14" s="56">
+      <c r="O14" s="40">
         <v>719</v>
       </c>
-      <c r="P14" s="56">
+      <c r="P14" s="40">
         <v>727</v>
       </c>
-      <c r="Q14" s="56">
+      <c r="Q14" s="40">
         <v>733</v>
       </c>
-      <c r="R14" s="56">
+      <c r="R14" s="40">
         <v>2689</v>
       </c>
-      <c r="S14" s="56">
+      <c r="S14" s="40">
         <v>2693</v>
       </c>
-      <c r="T14" s="56">
+      <c r="T14" s="40">
         <v>2699</v>
       </c>
-      <c r="U14" s="56">
+      <c r="U14" s="40">
         <v>2707</v>
       </c>
-      <c r="V14" s="56">
+      <c r="V14" s="40">
         <v>2711</v>
       </c>
-      <c r="W14" s="56">
+      <c r="W14" s="40">
         <v>2713</v>
       </c>
     </row>
     <row r="15" spans="1:23">
-      <c r="A15" s="56" t="s">
+      <c r="A15" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="57">
+      <c r="B15" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>21774</v>
       </c>
-      <c r="C15" s="56">
+      <c r="C15" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D15" s="56">
+      <c r="D15" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.66448974609375</v>
       </c>
-      <c r="E15" s="56">
+      <c r="E15" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>3</v>
       </c>
-      <c r="G15" s="56">
+      <c r="G15" s="40">
         <v>14</v>
       </c>
-      <c r="H15" s="56">
+      <c r="H15" s="40">
         <v>739</v>
       </c>
-      <c r="I15" s="56">
+      <c r="I15" s="40">
         <v>743</v>
       </c>
-      <c r="J15" s="56">
+      <c r="J15" s="40">
         <v>751</v>
       </c>
-      <c r="K15" s="56">
+      <c r="K15" s="40">
         <v>757</v>
       </c>
-      <c r="L15" s="56">
+      <c r="L15" s="40">
         <v>761</v>
       </c>
-      <c r="M15" s="56">
+      <c r="M15" s="40">
         <v>769</v>
       </c>
-      <c r="N15" s="56">
+      <c r="N15" s="40">
         <v>773</v>
       </c>
-      <c r="O15" s="56">
+      <c r="O15" s="40">
         <v>787</v>
       </c>
-      <c r="P15" s="56">
+      <c r="P15" s="40">
         <v>797</v>
       </c>
-      <c r="Q15" s="56">
+      <c r="Q15" s="40">
         <v>809</v>
       </c>
-      <c r="R15" s="56">
+      <c r="R15" s="40">
         <v>2749</v>
       </c>
-      <c r="S15" s="56">
+      <c r="S15" s="40">
         <v>2753</v>
       </c>
-      <c r="T15" s="56">
+      <c r="T15" s="40">
         <v>2767</v>
       </c>
-      <c r="U15" s="56">
+      <c r="U15" s="40">
         <v>2777</v>
       </c>
-      <c r="V15" s="56">
+      <c r="V15" s="40">
         <v>2789</v>
       </c>
-      <c r="W15" s="56">
+      <c r="W15" s="40">
         <v>2791</v>
       </c>
     </row>
     <row r="16" spans="1:23">
-      <c r="A16" s="56" t="s">
+      <c r="A16" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="57">
+      <c r="B16" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>11055</v>
       </c>
-      <c r="C16" s="56">
+      <c r="C16" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D16" s="56">
+      <c r="D16" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.337371826171875</v>
       </c>
-      <c r="E16" s="56">
+      <c r="E16" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
-      <c r="G16" s="56">
+      <c r="G16" s="40">
         <v>15</v>
       </c>
-      <c r="H16" s="56">
+      <c r="H16" s="40">
         <v>811</v>
       </c>
-      <c r="I16" s="56">
+      <c r="I16" s="40">
         <v>821</v>
       </c>
-      <c r="J16" s="56">
+      <c r="J16" s="40">
         <v>823</v>
       </c>
-      <c r="K16" s="56">
+      <c r="K16" s="40">
         <v>827</v>
       </c>
-      <c r="L16" s="56">
+      <c r="L16" s="40">
         <v>829</v>
       </c>
-      <c r="M16" s="56">
+      <c r="M16" s="40">
         <v>839</v>
       </c>
-      <c r="N16" s="56">
+      <c r="N16" s="40">
         <v>853</v>
       </c>
-      <c r="O16" s="56">
+      <c r="O16" s="40">
         <v>857</v>
       </c>
-      <c r="P16" s="56">
+      <c r="P16" s="40">
         <v>859</v>
       </c>
-      <c r="Q16" s="56">
+      <c r="Q16" s="40">
         <v>863</v>
       </c>
-      <c r="R16" s="56">
+      <c r="R16" s="40">
         <v>2833</v>
       </c>
-      <c r="S16" s="56">
+      <c r="S16" s="40">
         <v>2837</v>
       </c>
-      <c r="T16" s="56">
+      <c r="T16" s="40">
         <v>2843</v>
       </c>
-      <c r="U16" s="56">
+      <c r="U16" s="40">
         <v>2851</v>
       </c>
-      <c r="V16" s="56">
+      <c r="V16" s="40">
         <v>2857</v>
       </c>
-      <c r="W16" s="56">
+      <c r="W16" s="40">
         <v>2861</v>
       </c>
     </row>
     <row r="17" spans="1:23">
-      <c r="A17" s="56" t="s">
+      <c r="A17" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="57">
+      <c r="B17" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>25916</v>
       </c>
-      <c r="C17" s="56">
+      <c r="C17" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D17" s="56">
+      <c r="D17" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.7908935546875</v>
       </c>
-      <c r="E17" s="56">
+      <c r="E17" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>4</v>
       </c>
-      <c r="G17" s="56">
+      <c r="G17" s="40">
         <v>16</v>
       </c>
-      <c r="H17" s="56">
+      <c r="H17" s="40">
         <v>877</v>
       </c>
-      <c r="I17" s="56">
+      <c r="I17" s="40">
         <v>881</v>
       </c>
-      <c r="J17" s="56">
+      <c r="J17" s="40">
         <v>883</v>
       </c>
-      <c r="K17" s="56">
+      <c r="K17" s="40">
         <v>887</v>
       </c>
-      <c r="L17" s="56">
+      <c r="L17" s="40">
         <v>907</v>
       </c>
-      <c r="M17" s="56">
+      <c r="M17" s="40">
         <v>911</v>
       </c>
-      <c r="N17" s="56">
+      <c r="N17" s="40">
         <v>919</v>
       </c>
-      <c r="O17" s="56">
+      <c r="O17" s="40">
         <v>929</v>
       </c>
-      <c r="P17" s="56">
+      <c r="P17" s="40">
         <v>937</v>
       </c>
-      <c r="Q17" s="56">
+      <c r="Q17" s="40">
         <v>941</v>
       </c>
-      <c r="R17" s="56">
+      <c r="R17" s="40">
         <v>2909</v>
       </c>
-      <c r="S17" s="56">
+      <c r="S17" s="40">
         <v>2917</v>
       </c>
-      <c r="T17" s="56">
+      <c r="T17" s="40">
         <v>2927</v>
       </c>
-      <c r="U17" s="56">
+      <c r="U17" s="40">
         <v>2939</v>
       </c>
-      <c r="V17" s="56">
+      <c r="V17" s="40">
         <v>2953</v>
       </c>
-      <c r="W17" s="56">
+      <c r="W17" s="40">
         <v>2957</v>
       </c>
     </row>
     <row r="18" spans="1:23">
-      <c r="A18" s="56" t="s">
+      <c r="A18" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="57">
+      <c r="B18" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>4805</v>
       </c>
-      <c r="C18" s="56">
+      <c r="C18" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D18" s="56">
+      <c r="D18" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.146636962890625</v>
       </c>
-      <c r="E18" s="56">
+      <c r="E18" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:23">
-      <c r="A19" s="56" t="s">
+      <c r="A19" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="57">
+      <c r="B19" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>13338</v>
       </c>
-      <c r="C19" s="56">
+      <c r="C19" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D19" s="56">
+      <c r="D19" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.40704345703125</v>
       </c>
-      <c r="E19" s="56">
+      <c r="E19" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
-      <c r="H19" s="58">
+      <c r="H19" s="42">
         <f ca="1">10+SUM(C12:C21)*5</f>
         <v>35</v>
       </c>
-      <c r="I19" s="59">
+      <c r="I19" s="43">
         <f ca="1">2+MOD(E$17+A6,5)</f>
         <v>2</v>
       </c>
-      <c r="J19" s="59" t="b">
+      <c r="J19" s="43" t="b">
         <f ca="1">IF(I19&gt;=5,TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="K19" s="59"/>
+      <c r="K19" s="43"/>
     </row>
     <row r="20" spans="1:23">
-      <c r="A20" s="56" t="s">
+      <c r="A20" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="57">
+      <c r="B20" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>19275</v>
       </c>
-      <c r="C20" s="56">
+      <c r="C20" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D20" s="56">
+      <c r="D20" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.588226318359375</v>
       </c>
-      <c r="E20" s="56">
+      <c r="E20" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>3</v>
       </c>
-      <c r="H20" s="58">
+      <c r="H20" s="42">
         <f ca="1">20+SUM(C23:C32)*5</f>
         <v>50</v>
       </c>
-      <c r="I20" s="59">
+      <c r="I20" s="43">
         <f t="shared" ref="I20:I23" ca="1" si="7">2+MOD(E$17+A7,5)</f>
         <v>3</v>
       </c>
-      <c r="J20" s="59" t="b">
+      <c r="J20" s="43" t="b">
         <f t="shared" ref="J20:J23" ca="1" si="8">IF(I20&gt;=5,TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="K20" s="59"/>
+      <c r="K20" s="43"/>
     </row>
     <row r="21" spans="1:23">
-      <c r="A21" s="56" t="s">
+      <c r="A21" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="57">
+      <c r="B21" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>6440</v>
       </c>
-      <c r="C21" s="56">
+      <c r="C21" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D21" s="56">
+      <c r="D21" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.196533203125</v>
       </c>
-      <c r="E21" s="56">
+      <c r="E21" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="H21" s="58">
+      <c r="H21" s="42">
         <f ca="1">30+SUM(C33:C42)*5</f>
         <v>40</v>
       </c>
-      <c r="I21" s="59">
+      <c r="I21" s="43">
         <f t="shared" ca="1" si="7"/>
         <v>4</v>
       </c>
-      <c r="J21" s="59" t="b">
+      <c r="J21" s="43" t="b">
         <f t="shared" ca="1" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:23">
-      <c r="A22" s="56" t="s">
+      <c r="A22" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="57">
+      <c r="B22" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>5697</v>
       </c>
-      <c r="C22" s="56">
+      <c r="C22" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D22" s="56">
+      <c r="D22" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.173858642578125</v>
       </c>
-      <c r="E22" s="56">
+      <c r="E22" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="H22" s="58"/>
-      <c r="I22" s="59">
+      <c r="H22" s="42"/>
+      <c r="I22" s="43">
         <f t="shared" ca="1" si="7"/>
         <v>5</v>
       </c>
-      <c r="J22" s="59" t="b">
+      <c r="J22" s="43" t="b">
         <f t="shared" ca="1" si="8"/>
         <v>1</v>
       </c>
-      <c r="M22" s="57"/>
+      <c r="M22" s="41"/>
     </row>
     <row r="23" spans="1:23">
-      <c r="A23" s="56" t="s">
+      <c r="A23" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="57">
+      <c r="B23" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>30694</v>
       </c>
-      <c r="C23" s="56">
+      <c r="C23" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D23" s="56">
+      <c r="D23" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.93670654296875</v>
       </c>
-      <c r="E23" s="56">
+      <c r="E23" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>4</v>
       </c>
-      <c r="H23" s="58"/>
-      <c r="I23" s="59">
+      <c r="H23" s="42"/>
+      <c r="I23" s="43">
         <f t="shared" ca="1" si="7"/>
         <v>6</v>
       </c>
-      <c r="J23" s="59" t="b">
+      <c r="J23" s="43" t="b">
         <f t="shared" ca="1" si="8"/>
         <v>1</v>
       </c>
-      <c r="M23" s="57"/>
+      <c r="M23" s="41"/>
     </row>
     <row r="24" spans="1:23">
-      <c r="A24" s="56" t="s">
+      <c r="A24" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="57">
+      <c r="B24" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>20775</v>
       </c>
-      <c r="C24" s="56">
+      <c r="C24" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D24" s="56">
+      <c r="D24" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.634002685546875</v>
       </c>
-      <c r="E24" s="56">
+      <c r="E24" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>3</v>
       </c>
-      <c r="H24" s="60"/>
-      <c r="I24" s="59"/>
-      <c r="J24" s="59"/>
-      <c r="K24" s="59"/>
-      <c r="M24" s="57"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+      <c r="M24" s="41"/>
     </row>
     <row r="25" spans="1:23">
-      <c r="A25" s="56" t="s">
+      <c r="A25" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="57">
+      <c r="B25" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>8148</v>
       </c>
-      <c r="C25" s="56">
+      <c r="C25" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D25" s="56">
+      <c r="D25" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.2486572265625</v>
       </c>
-      <c r="E25" s="56">
+      <c r="E25" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="H25" s="58"/>
-      <c r="I25" s="59"/>
-      <c r="J25" s="59"/>
-      <c r="K25" s="59"/>
-      <c r="M25" s="57"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+      <c r="M25" s="41"/>
     </row>
     <row r="26" spans="1:23">
-      <c r="A26" s="56" t="s">
+      <c r="A26" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="57">
+      <c r="B26" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>21885</v>
       </c>
-      <c r="C26" s="56">
+      <c r="C26" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D26" s="56">
+      <c r="D26" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.667877197265625</v>
       </c>
-      <c r="E26" s="56">
+      <c r="E26" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>3</v>
       </c>
-      <c r="H26" s="58"/>
-      <c r="M26" s="57"/>
+      <c r="H26" s="42"/>
+      <c r="M26" s="41"/>
     </row>
     <row r="27" spans="1:23">
-      <c r="A27" s="56" t="s">
+      <c r="A27" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="57">
+      <c r="B27" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>11378</v>
       </c>
-      <c r="C27" s="56">
+      <c r="C27" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D27" s="56">
+      <c r="D27" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.34722900390625</v>
       </c>
-      <c r="E27" s="56">
+      <c r="E27" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
-      <c r="L27" s="57"/>
+      <c r="L27" s="41"/>
     </row>
     <row r="28" spans="1:23">
-      <c r="A28" s="56" t="s">
+      <c r="A28" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="57">
+      <c r="B28" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>22723</v>
       </c>
-      <c r="C28" s="56">
+      <c r="C28" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D28" s="56">
+      <c r="D28" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.693450927734375</v>
       </c>
-      <c r="E28" s="56">
+      <c r="E28" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>3</v>
       </c>
-      <c r="M28" s="57"/>
+      <c r="M28" s="41"/>
     </row>
     <row r="29" spans="1:23">
-      <c r="A29" s="56" t="s">
+      <c r="A29" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="57">
+      <c r="B29" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>25920</v>
       </c>
-      <c r="C29" s="56">
+      <c r="C29" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D29" s="56">
+      <c r="D29" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.791015625</v>
       </c>
-      <c r="E29" s="56">
+      <c r="E29" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>4</v>
       </c>
-      <c r="M29" s="57"/>
+      <c r="M29" s="41"/>
     </row>
     <row r="30" spans="1:23">
-      <c r="A30" s="56" t="s">
+      <c r="A30" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="B30" s="57">
+      <c r="B30" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>19577</v>
       </c>
-      <c r="C30" s="56">
+      <c r="C30" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D30" s="56">
+      <c r="D30" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.597442626953125</v>
       </c>
-      <c r="E30" s="56">
+      <c r="E30" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>3</v>
       </c>
-      <c r="M30" s="57"/>
+      <c r="M30" s="41"/>
     </row>
     <row r="31" spans="1:23">
-      <c r="A31" s="56" t="s">
+      <c r="A31" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="57">
+      <c r="B31" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>7614</v>
       </c>
-      <c r="C31" s="56">
+      <c r="C31" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D31" s="56">
+      <c r="D31" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.23236083984375</v>
       </c>
-      <c r="E31" s="56">
+      <c r="E31" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="M31" s="57"/>
+      <c r="M31" s="41"/>
     </row>
     <row r="32" spans="1:23">
-      <c r="A32" s="56" t="s">
+      <c r="A32" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="B32" s="57">
+      <c r="B32" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>15903</v>
       </c>
-      <c r="C32" s="56">
+      <c r="C32" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D32" s="56">
+      <c r="D32" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.485321044921875</v>
       </c>
-      <c r="E32" s="56">
+      <c r="E32" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
-      <c r="M32" s="57"/>
+      <c r="M32" s="41"/>
     </row>
     <row r="33" spans="1:13">
-      <c r="A33" s="56" t="s">
+      <c r="A33" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="B33" s="57">
+      <c r="B33" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>5484</v>
       </c>
-      <c r="C33" s="56">
+      <c r="C33" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D33" s="56">
+      <c r="D33" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.1673583984375</v>
       </c>
-      <c r="E33" s="56">
+      <c r="E33" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="M33" s="57"/>
+      <c r="M33" s="41"/>
     </row>
     <row r="34" spans="1:13">
-      <c r="A34" s="56" t="s">
+      <c r="A34" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="B34" s="57">
+      <c r="B34" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>14133</v>
       </c>
-      <c r="C34" s="56">
+      <c r="C34" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D34" s="56">
+      <c r="D34" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.431304931640625</v>
       </c>
-      <c r="E34" s="56">
+      <c r="E34" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
-      <c r="M34" s="57"/>
+      <c r="M34" s="41"/>
     </row>
     <row r="35" spans="1:13">
-      <c r="A35" s="56" t="s">
+      <c r="A35" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="B35" s="57">
+      <c r="B35" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>22474</v>
       </c>
-      <c r="C35" s="56">
+      <c r="C35" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D35" s="56">
+      <c r="D35" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.68585205078125</v>
       </c>
-      <c r="E35" s="56">
+      <c r="E35" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>3</v>
       </c>
-      <c r="M35" s="57"/>
+      <c r="M35" s="41"/>
     </row>
     <row r="36" spans="1:13">
-      <c r="A36" s="56" t="s">
+      <c r="A36" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="B36" s="57">
+      <c r="B36" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>7483</v>
       </c>
-      <c r="C36" s="56">
+      <c r="C36" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D36" s="56">
+      <c r="D36" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.228363037109375</v>
       </c>
-      <c r="E36" s="56">
+      <c r="E36" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="M36" s="57"/>
+      <c r="M36" s="41"/>
     </row>
     <row r="37" spans="1:13">
-      <c r="A37" s="56" t="s">
+      <c r="A37" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="B37" s="57">
+      <c r="B37" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>7256</v>
       </c>
-      <c r="C37" s="56">
+      <c r="C37" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D37" s="56">
+      <c r="D37" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.221435546875</v>
       </c>
-      <c r="E37" s="56">
+      <c r="E37" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="M37" s="57"/>
+      <c r="M37" s="41"/>
     </row>
     <row r="38" spans="1:13">
-      <c r="A38" s="56" t="s">
+      <c r="A38" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="B38" s="57">
+      <c r="B38" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>4529</v>
       </c>
-      <c r="C38" s="56">
+      <c r="C38" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D38" s="56">
+      <c r="D38" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.138214111328125</v>
       </c>
-      <c r="E38" s="56">
+      <c r="E38" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="M38" s="57"/>
+      <c r="M38" s="41"/>
     </row>
     <row r="39" spans="1:13">
-      <c r="A39" s="56" t="s">
+      <c r="A39" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="B39" s="57">
+      <c r="B39" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>9878</v>
       </c>
-      <c r="C39" s="56">
+      <c r="C39" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D39" s="56">
+      <c r="D39" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.30145263671875</v>
       </c>
-      <c r="E39" s="56">
+      <c r="E39" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
-      <c r="M39" s="57"/>
+      <c r="M39" s="41"/>
     </row>
     <row r="40" spans="1:13">
-      <c r="A40" s="56" t="s">
+      <c r="A40" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="B40" s="57">
+      <c r="B40" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>21015</v>
       </c>
-      <c r="C40" s="56">
+      <c r="C40" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D40" s="56">
+      <c r="D40" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.641326904296875</v>
       </c>
-      <c r="E40" s="56">
+      <c r="E40" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>3</v>
       </c>
-      <c r="M40" s="57"/>
+      <c r="M40" s="41"/>
     </row>
     <row r="41" spans="1:13">
-      <c r="A41" s="56" t="s">
+      <c r="A41" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="B41" s="57">
+      <c r="B41" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>9732</v>
       </c>
-      <c r="C41" s="56">
+      <c r="C41" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D41" s="56">
+      <c r="D41" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.2969970703125</v>
       </c>
-      <c r="E41" s="56">
+      <c r="E41" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
-      <c r="M41" s="57"/>
+      <c r="M41" s="41"/>
     </row>
     <row r="42" spans="1:13">
-      <c r="A42" s="56" t="s">
+      <c r="A42" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="B42" s="57">
+      <c r="B42" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>6125</v>
       </c>
-      <c r="C42" s="56">
+      <c r="C42" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D42" s="56">
+      <c r="D42" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.186920166015625</v>
       </c>
-      <c r="E42" s="56">
+      <c r="E42" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="M42" s="57"/>
+      <c r="M42" s="41"/>
     </row>
     <row r="43" spans="1:13">
-      <c r="A43" s="56" t="s">
+      <c r="A43" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="B43" s="57">
+      <c r="B43" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>5666</v>
       </c>
-      <c r="C43" s="56">
+      <c r="C43" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D43" s="56">
+      <c r="D43" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.17291259765625</v>
       </c>
-      <c r="E43" s="56">
+      <c r="E43" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="M43" s="57"/>
+      <c r="M43" s="41"/>
     </row>
     <row r="44" spans="1:13">
-      <c r="A44" s="56" t="s">
+      <c r="A44" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="B44" s="57">
+      <c r="B44" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>30899</v>
       </c>
-      <c r="C44" s="56">
+      <c r="C44" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D44" s="56">
+      <c r="D44" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.942962646484375</v>
       </c>
-      <c r="E44" s="56">
+      <c r="E44" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>4</v>
       </c>
-      <c r="M44" s="57"/>
+      <c r="M44" s="41"/>
     </row>
     <row r="45" spans="1:13">
-      <c r="A45" s="56" t="s">
+      <c r="A45" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="B45" s="57">
+      <c r="B45" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>7792</v>
       </c>
-      <c r="C45" s="56">
+      <c r="C45" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D45" s="56">
+      <c r="D45" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.23779296875</v>
       </c>
-      <c r="E45" s="56">
+      <c r="E45" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="M45" s="57"/>
+      <c r="M45" s="41"/>
     </row>
     <row r="46" spans="1:13">
-      <c r="A46" s="56" t="s">
+      <c r="A46" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="B46" s="57">
+      <c r="B46" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>17897</v>
       </c>
-      <c r="C46" s="56">
+      <c r="C46" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D46" s="56">
+      <c r="D46" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.546173095703125</v>
       </c>
-      <c r="E46" s="56">
+      <c r="E46" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:13">
-      <c r="A47" s="56" t="s">
+      <c r="A47" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="B47" s="57">
+      <c r="B47" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>29294</v>
       </c>
-      <c r="C47" s="56">
+      <c r="C47" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D47" s="56">
+      <c r="D47" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.89398193359375</v>
       </c>
-      <c r="E47" s="56">
+      <c r="E47" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:13">
-      <c r="A48" s="56" t="s">
+      <c r="A48" s="40" t="s">
         <v>75</v>
       </c>
-      <c r="B48" s="57">
+      <c r="B48" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>27919</v>
       </c>
-      <c r="C48" s="56">
+      <c r="C48" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D48" s="56">
+      <c r="D48" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.852020263671875</v>
       </c>
-      <c r="E48" s="56">
+      <c r="E48" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="56" t="s">
+      <c r="A49" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="B49" s="57">
+      <c r="B49" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>12700</v>
       </c>
-      <c r="C49" s="56">
+      <c r="C49" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D49" s="56">
+      <c r="D49" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.3875732421875</v>
       </c>
-      <c r="E49" s="56">
+      <c r="E49" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="56" t="s">
+      <c r="A50" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="B50" s="57">
+      <c r="B50" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>22437</v>
       </c>
-      <c r="C50" s="56">
+      <c r="C50" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D50" s="56">
+      <c r="D50" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.684722900390625</v>
       </c>
-      <c r="E50" s="56">
+      <c r="E50" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="56" t="s">
+      <c r="A51" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="B51" s="57">
+      <c r="B51" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>18298</v>
       </c>
-      <c r="C51" s="56">
+      <c r="C51" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D51" s="56">
+      <c r="D51" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.55841064453125</v>
       </c>
-      <c r="E51" s="56">
+      <c r="E51" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="56" t="s">
+      <c r="A52" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="B52" s="57">
+      <c r="B52" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>19243</v>
       </c>
-      <c r="C52" s="56">
+      <c r="C52" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D52" s="56">
+      <c r="D52" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.587249755859375</v>
       </c>
-      <c r="E52" s="56">
+      <c r="E52" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="56" t="s">
+      <c r="A53" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="B53" s="57">
+      <c r="B53" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>19336</v>
       </c>
-      <c r="C53" s="56">
+      <c r="C53" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D53" s="56">
+      <c r="D53" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.590087890625</v>
       </c>
-      <c r="E53" s="56">
+      <c r="E53" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="56" t="s">
+      <c r="A54" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="B54" s="57">
+      <c r="B54" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>18721</v>
       </c>
-      <c r="C54" s="56">
+      <c r="C54" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D54" s="56">
+      <c r="D54" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.571319580078125</v>
       </c>
-      <c r="E54" s="56">
+      <c r="E54" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="56" t="s">
+      <c r="A55" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="B55" s="57">
+      <c r="B55" s="41">
         <f t="shared" ca="1" si="3"/>
         <v>24902</v>
       </c>
-      <c r="C55" s="56">
+      <c r="C55" s="40">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D55" s="56">
+      <c r="D55" s="40">
         <f t="shared" ca="1" si="5"/>
         <v>0.75994873046875</v>
       </c>
-      <c r="E55" s="56">
+      <c r="E55" s="40">
         <f t="shared" ca="1" si="6"/>
         <v>4</v>
       </c>
@@ -4650,55 +4713,55 @@
   <sheetFormatPr defaultRowHeight="15.75"/>
   <sheetData>
     <row r="4" spans="3:7">
-      <c r="C4" s="55" t="s">
+      <c r="C4" s="71" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
     </row>
     <row r="5" spans="3:7">
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
     </row>
     <row r="6" spans="3:7">
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
-      <c r="F6" s="55"/>
-      <c r="G6" s="55"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
     </row>
     <row r="7" spans="3:7">
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="71"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="71"/>
     </row>
     <row r="8" spans="3:7">
-      <c r="C8" s="55"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="55"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="55"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="71"/>
+      <c r="E8" s="71"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
     </row>
     <row r="9" spans="3:7">
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="55"/>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
     </row>
     <row r="10" spans="3:7">
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
-      <c r="F10" s="55"/>
-      <c r="G10" s="55"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
     </row>
   </sheetData>
   <customSheetViews>
@@ -4727,15 +4790,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C289946819CFF499E91D197BC975371" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="674b7a4e239a9748c7aaa97e309327a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cca9fd2d-ef84-45c9-8063-8f4bd4c29606" xmlns:ns3="18557d39-01b8-4d71-9479-3fad465290ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="600253478e594d1349e02792803dc53a" ns2:_="" ns3:_="">
     <xsd:import namespace="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
@@ -4952,6 +5006,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF39485D-C01E-4ECC-A97D-DD7E1E83D4C0}">
   <ds:schemaRefs>
@@ -4963,13 +5026,28 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90817591-2806-4B51-9D1C-6BC766992EA6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
+    <ds:schemaRef ds:uri="18557d39-01b8-4d71-9479-3fad465290ae"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE888125-757F-4287-A413-B81F0A459F37}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90817591-2806-4B51-9D1C-6BC766992EA6}"/>
 </file>